--- a/AtchisonRegime/Outputs/Aust/ASX300_Real_Estate/df_regTrendSummaryASX300_Real_Estate.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Real_Estate/df_regTrendSummaryASX300_Real_Estate.xlsx
@@ -824,13 +824,13 @@
         <v>45351</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06724977616229189</v>
+        <v>0.01560353545881421</v>
       </c>
     </row>
   </sheetData>
